--- a/data/HARMONIQCI_open_source_tools.xlsx
+++ b/data/HARMONIQCI_open_source_tools.xlsx
@@ -1779,7 +1779,7 @@
       </c>
       <c r="Q14" s="18" t="inlineStr">
         <is>
-          <t>page offline: not reachable (ProxyError)</t>
+          <t>page offline: not reachable (ConnectError)</t>
         </is>
       </c>
       <c r="R14" s="18" t="inlineStr">
@@ -1852,11 +1852,7 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="Q15" s="18" t="inlineStr">
-        <is>
-          <t>page offline: not reachable (ProxyError)</t>
-        </is>
-      </c>
+      <c r="Q15" s="18" t="inlineStr"/>
       <c r="R15" s="18" t="inlineStr">
         <is>
           <t>2026-10-14</t>
@@ -1927,7 +1923,7 @@
       </c>
       <c r="Q16" s="18" t="inlineStr">
         <is>
-          <t>repository not found on GitHub (or private and the token has no access)</t>
+          <t>not found on GitHub (or private and the token has no access)</t>
         </is>
       </c>
       <c r="R16" s="18" t="inlineStr">
@@ -2465,8 +2461,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K38"/>
+  <dimension ref="A1:L42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" style="19" min="12" max="12"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="37" t="inlineStr">
@@ -2522,6 +2521,11 @@
       <c r="K1" s="37" t="inlineStr">
         <is>
           <t>Comment</t>
+        </is>
+      </c>
+      <c r="L1" s="37" t="inlineStr">
+        <is>
+          <t>Source</t>
         </is>
       </c>
     </row>
@@ -4141,6 +4145,182 @@
       </c>
       <c r="J38" s="18" t="inlineStr"/>
       <c r="K38" s="18" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>qkd/gs020-interop-kms</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>https://forge.etsi.org/rep/qkd/gs020-interop-kms</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>OpenAPI description for ETSI GS QKD 020, Interoperable Key Management System API</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>qkd</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>GitLab (forge.etsi.org/rep)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>qkd/gs015-ctrl-int-sdn</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>https://forge.etsi.org/rep/qkd/gs015-ctrl-int-sdn</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>YANG model for ETSI GS QKD 015, specification of management interfaces between SDN-enabled QKD node and SDN controller</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="n">
+        <v>1</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>qkd</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>GitLab (forge.etsi.org/rep)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>qkd/gs004-app-int</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>https://forge.etsi.org/rep/qkd/gs004-app-int</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Sample implementations for ETSI GS QKD 004, specification of QKD Application Interface</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>qkd</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>GitLab (forge.etsi.org/rep)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>qkd/gs014-key-deliv</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>https://forge.etsi.org/rep/qkd/gs014-key-deliv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>OpenAPI description for ETSI GS QKD 014, QKD Key delivery API</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="n">
+        <v>1</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>qkd</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>GitLab (forge.etsi.org/rep)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/HARMONIQCI_open_source_tools.xlsx
+++ b/data/HARMONIQCI_open_source_tools.xlsx
@@ -816,7 +816,7 @@
       </c>
       <c r="R2" s="18" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>
@@ -894,7 +894,7 @@
       </c>
       <c r="R3" s="18" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>
@@ -977,7 +977,7 @@
       </c>
       <c r="R4" s="18" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>
@@ -1055,7 +1055,7 @@
       </c>
       <c r="R5" s="18" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>
@@ -1138,7 +1138,7 @@
       </c>
       <c r="R6" s="18" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>
@@ -1221,7 +1221,7 @@
       </c>
       <c r="R7" s="18" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="I8" s="21" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="J8" s="21" t="inlineStr">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="N8" s="18" t="inlineStr">
         <is>
-          <t>v1.3.0 (2026-10-10)</t>
+          <t>v1.3.1 (2026-10-17)</t>
         </is>
       </c>
       <c r="O8" s="18" t="inlineStr">
@@ -1300,11 +1300,16 @@
         </is>
       </c>
       <c r="P8" s="18" t="n">
-        <v>180</v>
+        <v>181</v>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>new release v1.3.1 (2026-10-17)</t>
+        </is>
       </c>
       <c r="R8" s="18" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1383,7 @@
         </is>
       </c>
       <c r="P9" s="18" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="Q9" s="18" t="inlineStr">
         <is>
@@ -1387,7 +1392,7 @@
       </c>
       <c r="R9" s="18" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>
@@ -1465,7 +1470,7 @@
       </c>
       <c r="R10" s="18" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>
@@ -1543,7 +1548,7 @@
       </c>
       <c r="R11" s="18" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>
@@ -1626,7 +1631,7 @@
       </c>
       <c r="R12" s="18" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>
@@ -1709,7 +1714,7 @@
       </c>
       <c r="R13" s="18" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1789,7 @@
       </c>
       <c r="R14" s="18" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>
@@ -1855,7 +1860,7 @@
       <c r="Q15" s="18" t="inlineStr"/>
       <c r="R15" s="18" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>
@@ -1928,7 +1933,7 @@
       </c>
       <c r="R16" s="18" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>
@@ -2461,7 +2466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L42"/>
+  <dimension ref="A1:L44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" style="19" min="12" max="12"/>
@@ -4083,7 +4088,7 @@
       </c>
       <c r="G37" s="18" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="H37" s="18" t="inlineStr">
@@ -4147,178 +4152,270 @@
       <c r="K38" s="18" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
+      <c r="A39" s="18" t="inlineStr">
         <is>
           <t>qkd/gs020-interop-kms</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B39" s="18" t="inlineStr">
         <is>
           <t>https://forge.etsi.org/rep/qkd/gs020-interop-kms</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C39" s="18" t="inlineStr">
         <is>
           <t>OpenAPI description for ETSI GS QKD 020, Interoperable Key Management System API</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="n">
+      <c r="D39" s="18" t="inlineStr"/>
+      <c r="E39" s="18" t="inlineStr"/>
+      <c r="F39" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="G39" s="18" t="inlineStr">
         <is>
           <t>2026-06-29</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="H39" s="18" t="inlineStr">
         <is>
           <t>qkd</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
+      <c r="I39" s="18" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr">
+      <c r="J39" s="18" t="inlineStr"/>
+      <c r="K39" s="18" t="inlineStr"/>
+      <c r="L39" s="18" t="inlineStr">
         <is>
           <t>GitLab (forge.etsi.org/rep)</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
+      <c r="A40" s="18" t="inlineStr">
         <is>
           <t>qkd/gs015-ctrl-int-sdn</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B40" s="18" t="inlineStr">
         <is>
           <t>https://forge.etsi.org/rep/qkd/gs015-ctrl-int-sdn</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C40" s="18" t="inlineStr">
         <is>
           <t>YANG model for ETSI GS QKD 015, specification of management interfaces between SDN-enabled QKD node and SDN controller</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="n">
+      <c r="D40" s="18" t="inlineStr"/>
+      <c r="E40" s="18" t="inlineStr"/>
+      <c r="F40" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="G40" s="18" t="inlineStr">
         <is>
           <t>2026-05-29</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
+      <c r="H40" s="18" t="inlineStr">
         <is>
           <t>qkd</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
+      <c r="I40" s="18" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr">
+      <c r="J40" s="18" t="inlineStr"/>
+      <c r="K40" s="18" t="inlineStr"/>
+      <c r="L40" s="18" t="inlineStr">
         <is>
           <t>GitLab (forge.etsi.org/rep)</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
+      <c r="A41" s="18" t="inlineStr">
         <is>
           <t>qkd/gs004-app-int</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B41" s="18" t="inlineStr">
         <is>
           <t>https://forge.etsi.org/rep/qkd/gs004-app-int</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C41" s="18" t="inlineStr">
         <is>
           <t>Sample implementations for ETSI GS QKD 004, specification of QKD Application Interface</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr"/>
-      <c r="F41" t="n">
+      <c r="D41" s="18" t="inlineStr"/>
+      <c r="E41" s="18" t="inlineStr"/>
+      <c r="F41" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="G41" s="18" t="inlineStr">
         <is>
           <t>2026-05-22</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
+      <c r="H41" s="18" t="inlineStr">
         <is>
           <t>qkd</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
+      <c r="I41" s="18" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr">
+      <c r="J41" s="18" t="inlineStr"/>
+      <c r="K41" s="18" t="inlineStr"/>
+      <c r="L41" s="18" t="inlineStr">
         <is>
           <t>GitLab (forge.etsi.org/rep)</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
+      <c r="A42" s="18" t="inlineStr">
         <is>
           <t>qkd/gs014-key-deliv</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B42" s="18" t="inlineStr">
         <is>
           <t>https://forge.etsi.org/rep/qkd/gs014-key-deliv</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C42" s="18" t="inlineStr">
         <is>
           <t>OpenAPI description for ETSI GS QKD 014, QKD Key delivery API</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr"/>
-      <c r="F42" t="n">
+      <c r="D42" s="18" t="inlineStr"/>
+      <c r="E42" s="18" t="inlineStr"/>
+      <c r="F42" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="G42" s="18" t="inlineStr">
         <is>
           <t>2025-11-26</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="H42" s="18" t="inlineStr">
         <is>
           <t>qkd</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
+      <c r="I42" s="18" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr">
+      <c r="J42" s="18" t="inlineStr"/>
+      <c r="K42" s="18" t="inlineStr"/>
+      <c r="L42" s="18" t="inlineStr">
         <is>
           <t>GitLab (forge.etsi.org/rep)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>jlorenz-eng/qkd-security-standardization</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>https://github.com/jlorenz-eng/qkd-security-standardization</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Comparative analysis of ISO/IEC 23837-1 and ETSI GS QKD 016 based on the Common Criteria security evaluation framework.</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>"ETSI GS QKD" in:name,description,readme</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>GitHub</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Paraxiom/pq-transport-gateway</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>https://github.com/Paraxiom/pq-transport-gateway</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Post-Quantum Transport Gateway — PQC-hardens the ETSI GS QKD 014 QKD key-delivery channel. MIT/Apache-2.0.</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Rust</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="n">
+        <v>1</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>"ETSI GS QKD" in:name,description,readme</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>GitHub</t>
         </is>
       </c>
     </row>
@@ -4333,7 +4430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4471,6 +4568,60 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>SeQUeNCe</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Last commit</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>SeQUeNCe</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Latest release</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>v1.3.0 (2026-10-10)</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>v1.3.1 (2026-10-17)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/HARMONIQCI_open_source_tools.xlsx
+++ b/data/HARMONIQCI_open_source_tools.xlsx
@@ -816,7 +816,7 @@
       </c>
       <c r="R2" s="18" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -894,7 +894,7 @@
       </c>
       <c r="R3" s="18" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -977,7 +977,7 @@
       </c>
       <c r="R4" s="18" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -1055,7 +1055,7 @@
       </c>
       <c r="R5" s="18" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -1134,11 +1134,11 @@
         </is>
       </c>
       <c r="P6" s="18" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="R6" s="18" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -1212,7 +1212,7 @@
         </is>
       </c>
       <c r="P7" s="18" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="Q7" s="18" t="inlineStr">
         <is>
@@ -1221,7 +1221,7 @@
       </c>
       <c r="R7" s="18" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="I8" s="21" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="J8" s="21" t="inlineStr">
@@ -1300,16 +1300,12 @@
         </is>
       </c>
       <c r="P8" s="18" t="n">
-        <v>181</v>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>new release v1.3.1 (2026-10-17)</t>
-        </is>
-      </c>
+        <v>183</v>
+      </c>
+      <c r="Q8" s="18" t="inlineStr"/>
       <c r="R8" s="18" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1379,7 @@
         </is>
       </c>
       <c r="P9" s="18" t="n">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="Q9" s="18" t="inlineStr">
         <is>
@@ -1392,7 +1388,7 @@
       </c>
       <c r="R9" s="18" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -1466,11 +1462,11 @@
         </is>
       </c>
       <c r="P10" s="18" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="R10" s="18" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -1548,7 +1544,7 @@
       </c>
       <c r="R11" s="18" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -1631,7 +1627,7 @@
       </c>
       <c r="R12" s="18" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1710,7 @@
       </c>
       <c r="R13" s="18" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -1789,7 +1785,7 @@
       </c>
       <c r="R14" s="18" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -1857,10 +1853,14 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="Q15" s="18" t="inlineStr"/>
+      <c r="Q15" s="18" t="inlineStr">
+        <is>
+          <t>page offline: not reachable (ConnectTimeout)</t>
+        </is>
+      </c>
       <c r="R15" s="18" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -1933,7 +1933,7 @@
       </c>
       <c r="R16" s="18" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -2466,7 +2466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L44"/>
+  <dimension ref="A1:L46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" style="19" min="12" max="12"/>
@@ -2735,7 +2735,7 @@
       </c>
       <c r="G6" s="18" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="H6" s="18" t="inlineStr">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="E26" s="18" t="inlineStr"/>
       <c r="F26" s="18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G26" s="18" t="inlineStr">
         <is>
@@ -4088,7 +4088,7 @@
       </c>
       <c r="G37" s="18" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="H37" s="18" t="inlineStr">
@@ -4328,92 +4328,188 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
+      <c r="A43" s="18" t="inlineStr">
         <is>
           <t>jlorenz-eng/qkd-security-standardization</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B43" s="18" t="inlineStr">
         <is>
           <t>https://github.com/jlorenz-eng/qkd-security-standardization</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C43" s="18" t="inlineStr">
         <is>
           <t>Comparative analysis of ISO/IEC 23837-1 and ETSI GS QKD 016 based on the Common Criteria security evaluation framework.</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr"/>
-      <c r="F43" t="n">
+      <c r="D43" s="18" t="inlineStr"/>
+      <c r="E43" s="18" t="inlineStr"/>
+      <c r="F43" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="G43" s="18" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
+      <c r="H43" s="18" t="inlineStr">
         <is>
           <t>"ETSI GS QKD" in:name,description,readme</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
+      <c r="I43" s="18" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr">
+      <c r="J43" s="18" t="inlineStr"/>
+      <c r="K43" s="18" t="inlineStr"/>
+      <c r="L43" s="18" t="inlineStr">
         <is>
           <t>GitHub</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
+      <c r="A44" s="18" t="inlineStr">
         <is>
           <t>Paraxiom/pq-transport-gateway</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B44" s="18" t="inlineStr">
         <is>
           <t>https://github.com/Paraxiom/pq-transport-gateway</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C44" s="18" t="inlineStr">
         <is>
           <t>Post-Quantum Transport Gateway — PQC-hardens the ETSI GS QKD 014 QKD key-delivery channel. MIT/Apache-2.0.</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="D44" s="18" t="inlineStr">
         <is>
           <t>Rust</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr"/>
-      <c r="F44" t="n">
+      <c r="E44" s="18" t="inlineStr"/>
+      <c r="F44" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="G44" s="18" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
+      <c r="H44" s="18" t="inlineStr">
         <is>
           <t>"ETSI GS QKD" in:name,description,readme</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
+      <c r="I44" s="18" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr">
+      <c r="J44" s="18" t="inlineStr"/>
+      <c r="K44" s="18" t="inlineStr"/>
+      <c r="L44" s="18" t="inlineStr">
+        <is>
+          <t>GitHub</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>FelipeMadson/pqc-hybrid-kms-mesh</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>https://github.com/FelipeMadson/pqc-hybrid-kms-mesh</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Post-Quantum Hybrid Key Management Service (KMS) &amp; ETSI GS QKD 014 Key Distribution Mesh for RNP Quantum-Safe Optical Networks (NIST FIPS 203 &amp; FIPS 204).</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Go</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>"ETSI GS QKD" in:name,description,readme</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>GitHub</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Tebogo-2005/Quantum-Key-Distribution-BB84-Network-Simulator-with-Quantum-Error-Correction-QEC-</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>https://github.com/Tebogo-2005/Quantum-Key-Distribution-BB84-Network-Simulator-with-Quantum-Error-Correction-QEC-</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>quantum key distribution network simulator in:name,description</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr">
         <is>
           <t>GitHub</t>
         </is>
@@ -4430,7 +4526,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4569,56 +4665,83 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="18" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="18" t="inlineStr">
         <is>
           <t>SeQUeNCe</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="18" t="inlineStr">
         <is>
           <t>Last commit</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="18" t="inlineStr">
         <is>
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" s="18" t="inlineStr">
         <is>
           <t>2026-10-17</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="18" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="18" t="inlineStr">
         <is>
           <t>SeQUeNCe</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="18" t="inlineStr">
         <is>
           <t>Latest release</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" s="18" t="inlineStr">
         <is>
           <t>v1.3.0 (2026-10-10)</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E7" s="18" t="inlineStr">
         <is>
           <t>v1.3.1 (2026-10-17)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>SeQUeNCe</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Last commit</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
